--- a/Reiting.xlsx
+++ b/Reiting.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Загрузка\reiting-main\reiting-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Загрузка\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21885" windowHeight="13230" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12495" windowHeight="11940" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Predmet" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="114">
   <si>
     <t>Школа</t>
   </si>
@@ -126,6 +126,45 @@
     <t>Общий итог</t>
   </si>
   <si>
+    <t>АЗЫМБАЕВА</t>
+  </si>
+  <si>
+    <t>АЙТБАЙ</t>
+  </si>
+  <si>
+    <t>АЛЬМЕНОВА</t>
+  </si>
+  <si>
+    <t>АЛЬНАЗИРОВА</t>
+  </si>
+  <si>
+    <t>АРЫНГАЗИНА</t>
+  </si>
+  <si>
+    <t>АХШАЛОВА</t>
+  </si>
+  <si>
+    <t>ИЛЬЯСОВА</t>
+  </si>
+  <si>
+    <t>ИТЕМГЕНОВ</t>
+  </si>
+  <si>
+    <t>КАБЫЛОВА</t>
+  </si>
+  <si>
+    <t>КАЗАНГАПОВ</t>
+  </si>
+  <si>
+    <t>КАЙДАРОВА</t>
+  </si>
+  <si>
+    <t>КОЖАГЕЛЬДИНОВА</t>
+  </si>
+  <si>
+    <t>МОМЫНОВ</t>
+  </si>
+  <si>
     <t>Химия</t>
   </si>
   <si>
@@ -138,6 +177,9 @@
     <t>Ин яз</t>
   </si>
   <si>
+    <t>история</t>
+  </si>
+  <si>
     <t>География</t>
   </si>
   <si>
@@ -325,15 +367,6 @@
   </si>
   <si>
     <t>Завуч</t>
-  </si>
-  <si>
-    <t>Учитель1</t>
-  </si>
-  <si>
-    <t>Учитель2</t>
-  </si>
-  <si>
-    <t>Учитель3</t>
   </si>
 </sst>
 </file>
@@ -929,7 +962,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AF7"/>
+  <dimension ref="A1:AF17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -948,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1093,7 +1126,7 @@
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -1165,10 +1198,10 @@
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D6" s="9">
         <v>1</v>
@@ -1180,7 +1213,7 @@
         <v>8</v>
       </c>
       <c r="G6" s="10">
-        <f t="shared" ref="G6:G7" si="0">SUM(E6-D6-F6)</f>
+        <f t="shared" ref="G6:G17" si="0">SUM(E6-D6-F6)</f>
         <v>-4.5</v>
       </c>
       <c r="H6" s="9"/>
@@ -1188,7 +1221,7 @@
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
       <c r="L6" s="11">
-        <f t="shared" ref="L6:L7" si="1">SUM(H6+I6+J6+K6)</f>
+        <f t="shared" ref="L6:L17" si="1">SUM(H6+I6+J6+K6)</f>
         <v>0</v>
       </c>
       <c r="M6" s="9"/>
@@ -1198,7 +1231,7 @@
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
       <c r="S6" s="12">
-        <f t="shared" ref="S6:S7" si="2">SUM(M6+N6+O6+P6+Q6+R6)</f>
+        <f t="shared" ref="S6:S17" si="2">SUM(M6+N6+O6+P6+Q6+R6)</f>
         <v>0</v>
       </c>
       <c r="T6" s="9"/>
@@ -1210,34 +1243,34 @@
         <v>-6</v>
       </c>
       <c r="Z6" s="13">
-        <f t="shared" ref="Z6:Z7" si="3">SUM(T6+U6+V6+W6+X6+Y6)</f>
+        <f t="shared" ref="Z6:Z17" si="3">SUM(T6+U6+V6+W6+X6+Y6)</f>
         <v>-6</v>
       </c>
       <c r="AA6" s="10">
-        <f t="shared" ref="AA6:AA7" si="4">SUM(G6)</f>
+        <f t="shared" ref="AA6:AA17" si="4">SUM(G6)</f>
         <v>-4.5</v>
       </c>
       <c r="AB6" s="11">
-        <f t="shared" ref="AB6:AB7" si="5">SUM(L6)</f>
+        <f t="shared" ref="AB6:AB17" si="5">SUM(L6)</f>
         <v>0</v>
       </c>
       <c r="AC6" s="12">
-        <f t="shared" ref="AC6:AC7" si="6">SUM(S6)</f>
+        <f t="shared" ref="AC6:AC17" si="6">SUM(S6)</f>
         <v>0</v>
       </c>
       <c r="AD6" s="13">
-        <f t="shared" ref="AD6:AD7" si="7">SUM(Z6)</f>
+        <f t="shared" ref="AD6:AD17" si="7">SUM(Z6)</f>
         <v>-6</v>
       </c>
       <c r="AE6" s="14">
-        <f t="shared" ref="AE6:AE7" si="8">SUM(G6+L6+S6+Z6)</f>
+        <f t="shared" ref="AE6:AE17" si="8">SUM(G6+L6+S6+Z6)</f>
         <v>-10.5</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -1304,6 +1337,726 @@
       <c r="AE7" s="14">
         <f t="shared" si="8"/>
         <v>-11.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="E8" s="9">
+        <v>4.8</v>
+      </c>
+      <c r="F8" s="9">
+        <v>5</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" si="0"/>
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9">
+        <v>-6</v>
+      </c>
+      <c r="Z8" s="13">
+        <f t="shared" si="3"/>
+        <v>-6</v>
+      </c>
+      <c r="AA8" s="10">
+        <f t="shared" si="4"/>
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="AB8" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC8" s="12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD8" s="13">
+        <f t="shared" si="7"/>
+        <v>-6</v>
+      </c>
+      <c r="AE8" s="14">
+        <f t="shared" si="8"/>
+        <v>-7.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E9" s="9">
+        <v>4.7</v>
+      </c>
+      <c r="F9" s="9">
+        <v>3</v>
+      </c>
+      <c r="G9" s="10">
+        <f t="shared" si="0"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="9">
+        <v>-6</v>
+      </c>
+      <c r="Z9" s="13">
+        <f t="shared" si="3"/>
+        <v>-6</v>
+      </c>
+      <c r="AA9" s="10">
+        <f t="shared" si="4"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="AB9" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC9" s="12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD9" s="13">
+        <f t="shared" si="7"/>
+        <v>-6</v>
+      </c>
+      <c r="AE9" s="14">
+        <f t="shared" si="8"/>
+        <v>-5.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A10" s="9"/>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="E10" s="9">
+        <v>4.7</v>
+      </c>
+      <c r="F10" s="9">
+        <v>4</v>
+      </c>
+      <c r="G10" s="10">
+        <f t="shared" si="0"/>
+        <v>-0.19999999999999973</v>
+      </c>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9"/>
+      <c r="Y10" s="9">
+        <v>-6</v>
+      </c>
+      <c r="Z10" s="13">
+        <f t="shared" si="3"/>
+        <v>-6</v>
+      </c>
+      <c r="AA10" s="10">
+        <f t="shared" si="4"/>
+        <v>-0.19999999999999973</v>
+      </c>
+      <c r="AB10" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC10" s="12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD10" s="13">
+        <f t="shared" si="7"/>
+        <v>-6</v>
+      </c>
+      <c r="AE10" s="14">
+        <f t="shared" si="8"/>
+        <v>-6.1999999999999993</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A11" s="9"/>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="9">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F11" s="9">
+        <v>7</v>
+      </c>
+      <c r="G11" s="10">
+        <f t="shared" si="0"/>
+        <v>-3.4000000000000004</v>
+      </c>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9"/>
+      <c r="Y11" s="9">
+        <v>-6</v>
+      </c>
+      <c r="Z11" s="13">
+        <f t="shared" si="3"/>
+        <v>-6</v>
+      </c>
+      <c r="AA11" s="10">
+        <f t="shared" si="4"/>
+        <v>-3.4000000000000004</v>
+      </c>
+      <c r="AB11" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC11" s="12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="13">
+        <f t="shared" si="7"/>
+        <v>-6</v>
+      </c>
+      <c r="AE11" s="14">
+        <f t="shared" si="8"/>
+        <v>-9.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A12" s="9"/>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="E12" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="F12" s="9">
+        <v>10</v>
+      </c>
+      <c r="G12" s="10">
+        <f t="shared" si="0"/>
+        <v>-6.3</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9">
+        <v>-6</v>
+      </c>
+      <c r="Z12" s="13">
+        <f t="shared" si="3"/>
+        <v>-6</v>
+      </c>
+      <c r="AA12" s="10">
+        <f t="shared" si="4"/>
+        <v>-6.3</v>
+      </c>
+      <c r="AB12" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC12" s="12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD12" s="13">
+        <f t="shared" si="7"/>
+        <v>-6</v>
+      </c>
+      <c r="AE12" s="14">
+        <f t="shared" si="8"/>
+        <v>-12.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A13" s="9"/>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="E13" s="9">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F13" s="9">
+        <v>8</v>
+      </c>
+      <c r="G13" s="10">
+        <f t="shared" si="0"/>
+        <v>-4.8000000000000007</v>
+      </c>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="9">
+        <v>-6</v>
+      </c>
+      <c r="Z13" s="13">
+        <f t="shared" si="3"/>
+        <v>-6</v>
+      </c>
+      <c r="AA13" s="10">
+        <f t="shared" si="4"/>
+        <v>-4.8000000000000007</v>
+      </c>
+      <c r="AB13" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC13" s="12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD13" s="13">
+        <f t="shared" si="7"/>
+        <v>-6</v>
+      </c>
+      <c r="AE13" s="14">
+        <f t="shared" si="8"/>
+        <v>-10.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A14" s="9"/>
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E14" s="9">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F14" s="9">
+        <v>11</v>
+      </c>
+      <c r="G14" s="10">
+        <f t="shared" si="0"/>
+        <v>-7.1999999999999993</v>
+      </c>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="9"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9"/>
+      <c r="Y14" s="9">
+        <v>-6</v>
+      </c>
+      <c r="Z14" s="13">
+        <f t="shared" si="3"/>
+        <v>-6</v>
+      </c>
+      <c r="AA14" s="10">
+        <f t="shared" si="4"/>
+        <v>-7.1999999999999993</v>
+      </c>
+      <c r="AB14" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC14" s="12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD14" s="13">
+        <f t="shared" si="7"/>
+        <v>-6</v>
+      </c>
+      <c r="AE14" s="14">
+        <f t="shared" si="8"/>
+        <v>-13.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A15" s="9"/>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="E15" s="9">
+        <v>4.3</v>
+      </c>
+      <c r="F15" s="9">
+        <v>3</v>
+      </c>
+      <c r="G15" s="10">
+        <f t="shared" si="0"/>
+        <v>0.69999999999999973</v>
+      </c>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="9">
+        <v>-6</v>
+      </c>
+      <c r="Z15" s="13">
+        <f t="shared" si="3"/>
+        <v>-6</v>
+      </c>
+      <c r="AA15" s="10">
+        <f t="shared" si="4"/>
+        <v>0.69999999999999973</v>
+      </c>
+      <c r="AB15" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC15" s="12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD15" s="13">
+        <f t="shared" si="7"/>
+        <v>-6</v>
+      </c>
+      <c r="AE15" s="14">
+        <f t="shared" si="8"/>
+        <v>-5.3000000000000007</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A16" s="9"/>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E16" s="9">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F16" s="9">
+        <v>10</v>
+      </c>
+      <c r="G16" s="10">
+        <f t="shared" si="0"/>
+        <v>-6.6999999999999993</v>
+      </c>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="9"/>
+      <c r="Y16" s="9">
+        <v>-6</v>
+      </c>
+      <c r="Z16" s="13">
+        <f t="shared" si="3"/>
+        <v>-6</v>
+      </c>
+      <c r="AA16" s="10">
+        <f t="shared" si="4"/>
+        <v>-6.6999999999999993</v>
+      </c>
+      <c r="AB16" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="13">
+        <f t="shared" si="7"/>
+        <v>-6</v>
+      </c>
+      <c r="AE16" s="14">
+        <f t="shared" si="8"/>
+        <v>-12.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A17" s="9"/>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="9">
+        <v>1</v>
+      </c>
+      <c r="E17" s="9">
+        <v>4.3</v>
+      </c>
+      <c r="F17" s="9">
+        <v>8</v>
+      </c>
+      <c r="G17" s="10">
+        <f t="shared" si="0"/>
+        <v>-4.7</v>
+      </c>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9"/>
+      <c r="Y17" s="9">
+        <v>-6</v>
+      </c>
+      <c r="Z17" s="13">
+        <f t="shared" si="3"/>
+        <v>-6</v>
+      </c>
+      <c r="AA17" s="10">
+        <f t="shared" si="4"/>
+        <v>-4.7</v>
+      </c>
+      <c r="AB17" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC17" s="12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD17" s="13">
+        <f t="shared" si="7"/>
+        <v>-6</v>
+      </c>
+      <c r="AE17" s="14">
+        <f t="shared" si="8"/>
+        <v>-10.7</v>
       </c>
     </row>
   </sheetData>
@@ -1349,43 +2102,43 @@
         <v>3</v>
       </c>
       <c r="E1" s="29" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="F1" s="26" t="s">
         <v>11</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="J1" s="28" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="L1" s="31" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="M1" s="31" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="N1" s="31" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="O1" s="31" t="s">
         <v>22</v>
       </c>
       <c r="P1" s="31" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="Q1" s="31" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="R1" s="7" t="s">
         <v>23</v>
@@ -1406,19 +2159,19 @@
         <v>30</v>
       </c>
       <c r="X1" s="7" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="Y1" s="7" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="Z1" s="7" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="AA1" s="7" t="s">
         <v>23</v>
       </c>
       <c r="AB1" s="7" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="AC1" s="8" t="s">
         <v>32</v>
@@ -1498,10 +2251,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D4" s="22">
         <v>0.9</v>
@@ -1572,10 +2325,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D5" s="22">
         <v>0.9</v>
@@ -1636,10 +2389,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D6" s="22">
         <v>0.1</v>
@@ -1700,10 +2453,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D7" s="22">
         <v>0.3</v>
@@ -1764,10 +2517,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D8" s="22">
         <v>0.9</v>
@@ -1828,10 +2581,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D9" s="22">
         <v>0.7</v>
@@ -1842,61 +2595,49 @@
       <c r="F9" s="9">
         <v>4</v>
       </c>
-      <c r="G9" s="9">
-        <v>3</v>
-      </c>
-      <c r="H9" s="9">
-        <v>2</v>
-      </c>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
       <c r="I9" s="9"/>
       <c r="J9" s="10">
         <f t="shared" si="0"/>
-        <v>13.7</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
-      <c r="M9" s="9">
-        <v>2</v>
-      </c>
+      <c r="M9" s="9"/>
       <c r="N9" s="9"/>
       <c r="O9" s="9"/>
-      <c r="P9" s="9">
-        <v>2</v>
-      </c>
+      <c r="P9" s="9"/>
       <c r="Q9" s="9"/>
       <c r="R9" s="11">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S9" s="9"/>
-      <c r="T9" s="9">
-        <v>1</v>
-      </c>
+      <c r="T9" s="9"/>
       <c r="U9" s="9"/>
-      <c r="V9" s="9">
-        <v>2</v>
-      </c>
+      <c r="V9" s="9"/>
       <c r="W9" s="9"/>
       <c r="X9" s="9"/>
       <c r="Y9" s="12">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="10">
         <f t="shared" si="3"/>
-        <v>13.7</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AA9" s="11">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="12">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC9" s="14">
         <f t="shared" si="6"/>
-        <v>20.7</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
@@ -1904,7 +2645,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>5</v>
@@ -1968,7 +2709,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>5</v>
@@ -2032,10 +2773,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D12" s="22">
         <v>1.2</v>
@@ -2096,10 +2837,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D13" s="22">
         <v>0.8</v>
@@ -2160,10 +2901,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D14" s="22">
         <v>0.9</v>
@@ -2224,10 +2965,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D15" s="22">
         <v>0.9</v>
@@ -2288,7 +3029,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>5</v>
@@ -2352,10 +3093,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D17" s="23">
         <v>0.3</v>
@@ -2416,10 +3157,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D18" s="23">
         <v>0.7</v>
@@ -2480,10 +3221,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D19" s="23">
         <v>0.8</v>
@@ -2544,10 +3285,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D20" s="23">
         <v>0.1</v>
@@ -2608,10 +3349,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="D21" s="23">
         <v>0.1</v>
@@ -2672,10 +3413,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D22" s="23">
         <v>0.8</v>
@@ -2736,10 +3477,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="D23" s="23">
         <v>0.3</v>
@@ -2800,10 +3541,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="D24" s="23">
         <v>0.3</v>
@@ -2864,10 +3605,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D25" s="23">
         <v>0.9</v>
@@ -2928,7 +3669,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>5</v>
@@ -2992,10 +3733,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D27" s="23">
         <v>0.9</v>
@@ -3056,10 +3797,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D28" s="23">
         <v>1.2</v>
@@ -3120,10 +3861,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D29" s="23">
         <v>0.7</v>
@@ -3184,10 +3925,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D30" s="23">
         <v>1.2</v>
@@ -3248,7 +3989,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>5</v>
@@ -3312,10 +4053,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D32" s="23">
         <v>0.1</v>
@@ -3376,7 +4117,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>5</v>
@@ -3440,10 +4181,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D34" s="23">
         <v>0.1</v>
@@ -3504,10 +4245,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D35" s="23">
         <v>0.9</v>
@@ -3568,7 +4309,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>5</v>
@@ -3632,10 +4373,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D37" s="23">
         <v>0.1</v>
@@ -3696,10 +4437,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="D38" s="23">
         <v>0.1</v>
@@ -3757,10 +4498,10 @@
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D39" s="23">
         <v>0.7</v>
@@ -3818,10 +4559,10 @@
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" s="21" t="s">
         <v>86</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>72</v>
       </c>
       <c r="D40" s="23">
         <v>1.2</v>
